--- a/forms/trg/Formulir_TRG_ufrg.xlsx
+++ b/forms/trg/Formulir_TRG_ufrg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B19)</f>
+        <f>COUNTA(Anggota!B5:B22)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F19)</f>
+        <f>COUNTA(Anggota!F5:F22)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,25 +913,33 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Elly Wahyudin</t>
+          <t>Prof. Firzan Nainu, Ph.D.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>Department of Pharmacy, Faculty of Pharmacy, Universitas Hasanuddin</t>
+        </is>
+      </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>ellywahyudins@gmail.com</t>
+          <t>Pharmacology, Immunology, Virology</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-0989-4023</t>
+        </is>
+      </c>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="12" t="n"/>
       <c r="M5" s="11" t="inlineStr">
@@ -946,29 +954,25 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Mukarram Mudjahid</t>
+          <t>Elly Wahyudin</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>mukarrammudjahid@unhas.ac.id</t>
+          <t>ellywahyudins@gmail.com</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>0009-0009-5361-4712</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
@@ -983,25 +987,29 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Rangga Meidianto Asri</t>
+          <t>Mukarram Mudjahid</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>rangga.masri@farmasi.unhas.ac.id</t>
+          <t>mukarrammudjahid@unhas.ac.id</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="11" t="inlineStr">
+        <is>
+          <t>0009-0009-5361-4712</t>
+        </is>
+      </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="inlineStr">
@@ -1014,10 +1022,22 @@
       <c r="A8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Rangga Meidianto Asri</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>Lecturer</t>
+        </is>
+      </c>
       <c r="D8" s="12" t="n"/>
-      <c r="E8" s="11" t="n"/>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>rangga.masri@farmasi.unhas.ac.id</t>
+        </is>
+      </c>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
@@ -1025,16 +1045,32 @@
       <c r="J8" s="12" t="n"/>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
+      <c r="M8" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>About the Group Project</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11" t="n"/>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Our mission at the Unhas Fly Research Group (UFRG) is to advance the understanding of biological phenomena through the innovative use of Drosophila melanogaster . By leveraging the unique advantages of fly systems, we aim to contribute to the discovery of novel therapeutics and deepen our knowledge of fundamental biological processes that are relevant to human health.</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1042,16 +1078,32 @@
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="M9" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>About the Group Project</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D10" s="12" t="n"/>
-      <c r="E10" s="11" t="n"/>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>Our mission at the Unhas Fly Research Group (UFRG) is to advance the understanding of biological phenomena through the innovative use of Drosophila melanogaster . By leveraging the unique advantages of fly systems, we aim to contribute to the discovery of novel therapeutics and deepen our knowledge of fundamental biological processes that are relevant to human health.</t>
+        </is>
+      </c>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
@@ -1059,7 +1111,11 @@
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
+      <c r="M10" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -1214,15 +1270,66 @@
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="12" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
